--- a/livrables/temps_scenario_2.xlsx
+++ b/livrables/temps_scenario_2.xlsx
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>113.5</v>
+        <v>113.4</v>
       </c>
       <c r="G9" t="n">
         <v>10</v>
@@ -830,13 +830,13 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>123.5</v>
+        <v>123.4</v>
       </c>
       <c r="J9" t="n">
-        <v>123.5</v>
+        <v>123.4</v>
       </c>
       <c r="K9" t="n">
-        <v>123.5</v>
+        <v>123.4</v>
       </c>
       <c r="L9" t="n">
         <v>202.5</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>104.7</v>
+        <v>104.6</v>
       </c>
       <c r="G14" t="n">
         <v>10</v>
@@ -1040,13 +1040,13 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>114.7</v>
+        <v>114.6</v>
       </c>
       <c r="J14" t="n">
-        <v>114.7</v>
+        <v>114.6</v>
       </c>
       <c r="K14" t="n">
-        <v>114.7</v>
+        <v>114.6</v>
       </c>
       <c r="L14" t="n">
         <v>202.5</v>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G24" t="n">
         <v>8</v>
@@ -1460,13 +1460,13 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>85.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L24" t="n">
         <v>122</v>
@@ -1652,7 +1652,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1862,7 +1862,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>198.4</v>
+        <v>198.2</v>
       </c>
       <c r="G34" t="n">
         <v>22</v>
@@ -1880,13 +1880,13 @@
         <v>11</v>
       </c>
       <c r="I34" t="n">
-        <v>220.4</v>
+        <v>220.2</v>
       </c>
       <c r="J34" t="n">
-        <v>220.4</v>
+        <v>220.2</v>
       </c>
       <c r="K34" t="n">
-        <v>220.4</v>
+        <v>220.2</v>
       </c>
       <c r="L34" t="n">
         <v>275</v>
@@ -2072,7 +2072,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>172.4</v>
+        <v>172.2</v>
       </c>
       <c r="G39" t="n">
         <v>22</v>
@@ -2090,13 +2090,13 @@
         <v>11</v>
       </c>
       <c r="I39" t="n">
-        <v>194.4</v>
+        <v>194.2</v>
       </c>
       <c r="J39" t="n">
-        <v>194.4</v>
+        <v>194.2</v>
       </c>
       <c r="K39" t="n">
-        <v>194.4</v>
+        <v>194.2</v>
       </c>
       <c r="L39" t="n">
         <v>275</v>
@@ -2282,7 +2282,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>162.4</v>
+        <v>162</v>
       </c>
       <c r="G44" t="n">
         <v>22</v>
@@ -2300,13 +2300,13 @@
         <v>11</v>
       </c>
       <c r="I44" t="n">
-        <v>184.4</v>
+        <v>184</v>
       </c>
       <c r="J44" t="n">
-        <v>184.4</v>
+        <v>184</v>
       </c>
       <c r="K44" t="n">
-        <v>184.4</v>
+        <v>184</v>
       </c>
       <c r="L44" t="n">
         <v>275</v>
@@ -2492,7 +2492,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>226.3</v>
+        <v>226.1</v>
       </c>
       <c r="G49" t="n">
         <v>22</v>
@@ -2510,13 +2510,13 @@
         <v>11</v>
       </c>
       <c r="I49" t="n">
-        <v>248.3</v>
+        <v>248.1</v>
       </c>
       <c r="J49" t="n">
-        <v>248.3</v>
+        <v>248.1</v>
       </c>
       <c r="K49" t="n">
-        <v>248.3</v>
+        <v>248.1</v>
       </c>
       <c r="L49" t="n">
         <v>318</v>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>200.2</v>
+        <v>199.8</v>
       </c>
       <c r="G54" t="n">
         <v>22</v>
@@ -2720,13 +2720,13 @@
         <v>11</v>
       </c>
       <c r="I54" t="n">
-        <v>222.2</v>
+        <v>221.8</v>
       </c>
       <c r="J54" t="n">
-        <v>222.2</v>
+        <v>221.8</v>
       </c>
       <c r="K54" t="n">
-        <v>222.2</v>
+        <v>221.8</v>
       </c>
       <c r="L54" t="n">
         <v>318</v>
@@ -2912,7 +2912,7 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>189.9</v>
+        <v>189.5</v>
       </c>
       <c r="G59" t="n">
         <v>22</v>
@@ -2930,13 +2930,13 @@
         <v>11</v>
       </c>
       <c r="I59" t="n">
-        <v>211.9</v>
+        <v>211.5</v>
       </c>
       <c r="J59" t="n">
-        <v>211.9</v>
+        <v>211.5</v>
       </c>
       <c r="K59" t="n">
-        <v>211.9</v>
+        <v>211.5</v>
       </c>
       <c r="L59" t="n">
         <v>318</v>

--- a/livrables/temps_scenario_2.xlsx
+++ b/livrables/temps_scenario_2.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="temps_scenario_2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'temps_scenario_2'!$A$1:$L$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'temps_scenario_2'!$A$1:$L$73</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -724,11 +724,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -737,7 +737,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>121.5</v>
+        <v>132.6</v>
       </c>
       <c r="G7" t="n">
         <v>10</v>
@@ -746,13 +746,13 @@
         <v>5</v>
       </c>
       <c r="I7" t="n">
-        <v>131.5</v>
+        <v>142.6</v>
       </c>
       <c r="J7" t="n">
-        <v>131.5</v>
+        <v>142.6</v>
       </c>
       <c r="K7" t="n">
-        <v>131.5</v>
+        <v>142.6</v>
       </c>
       <c r="L7" t="n">
         <v>202.5</v>
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>117.2</v>
+        <v>121.5</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -788,13 +788,13 @@
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>127.2</v>
+        <v>131.5</v>
       </c>
       <c r="J8" t="n">
-        <v>127.2</v>
+        <v>131.5</v>
       </c>
       <c r="K8" t="n">
-        <v>127.2</v>
+        <v>131.5</v>
       </c>
       <c r="L8" t="n">
         <v>202.5</v>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>113.4</v>
+        <v>117.2</v>
       </c>
       <c r="G9" t="n">
         <v>10</v>
@@ -830,13 +830,13 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>123.4</v>
+        <v>127.2</v>
       </c>
       <c r="J9" t="n">
-        <v>123.4</v>
+        <v>127.2</v>
       </c>
       <c r="K9" t="n">
-        <v>123.4</v>
+        <v>127.2</v>
       </c>
       <c r="L9" t="n">
         <v>202.5</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>107.8</v>
+        <v>113.4</v>
       </c>
       <c r="G10" t="n">
         <v>10</v>
@@ -872,13 +872,13 @@
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>117.8</v>
+        <v>123.4</v>
       </c>
       <c r="J10" t="n">
-        <v>117.8</v>
+        <v>123.4</v>
       </c>
       <c r="K10" t="n">
-        <v>117.8</v>
+        <v>123.4</v>
       </c>
       <c r="L10" t="n">
         <v>202.5</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>106</v>
+        <v>110.9</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
@@ -914,13 +914,13 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>116</v>
+        <v>120.9</v>
       </c>
       <c r="J11" t="n">
-        <v>116</v>
+        <v>120.9</v>
       </c>
       <c r="K11" t="n">
-        <v>116</v>
+        <v>120.9</v>
       </c>
       <c r="L11" t="n">
         <v>202.5</v>
@@ -934,11 +934,11 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>116.1</v>
+        <v>107.8</v>
       </c>
       <c r="G12" t="n">
         <v>10</v>
@@ -956,13 +956,13 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>126.1</v>
+        <v>117.8</v>
       </c>
       <c r="J12" t="n">
-        <v>126.1</v>
+        <v>117.8</v>
       </c>
       <c r="K12" t="n">
-        <v>126.1</v>
+        <v>117.8</v>
       </c>
       <c r="L12" t="n">
         <v>202.5</v>
@@ -976,11 +976,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>109.7</v>
+        <v>106</v>
       </c>
       <c r="G13" t="n">
         <v>10</v>
@@ -998,13 +998,13 @@
         <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>119.7</v>
+        <v>116</v>
       </c>
       <c r="J13" t="n">
-        <v>119.7</v>
+        <v>116</v>
       </c>
       <c r="K13" t="n">
-        <v>119.7</v>
+        <v>116</v>
       </c>
       <c r="L13" t="n">
         <v>202.5</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>104.6</v>
+        <v>116.1</v>
       </c>
       <c r="G14" t="n">
         <v>10</v>
@@ -1040,13 +1040,13 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>114.6</v>
+        <v>126.1</v>
       </c>
       <c r="J14" t="n">
-        <v>114.6</v>
+        <v>126.1</v>
       </c>
       <c r="K14" t="n">
-        <v>114.6</v>
+        <v>126.1</v>
       </c>
       <c r="L14" t="n">
         <v>202.5</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>98.09999999999999</v>
+        <v>109.7</v>
       </c>
       <c r="G15" t="n">
         <v>10</v>
@@ -1082,13 +1082,13 @@
         <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>108.1</v>
+        <v>119.7</v>
       </c>
       <c r="J15" t="n">
-        <v>108.1</v>
+        <v>119.7</v>
       </c>
       <c r="K15" t="n">
-        <v>108.1</v>
+        <v>119.7</v>
       </c>
       <c r="L15" t="n">
         <v>202.5</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>95.7</v>
+        <v>104.6</v>
       </c>
       <c r="G16" t="n">
         <v>10</v>
@@ -1124,13 +1124,13 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>105.7</v>
+        <v>114.6</v>
       </c>
       <c r="J16" t="n">
-        <v>105.7</v>
+        <v>114.6</v>
       </c>
       <c r="K16" t="n">
-        <v>105.7</v>
+        <v>114.6</v>
       </c>
       <c r="L16" t="n">
         <v>202.5</v>
@@ -1139,16 +1139,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1157,40 +1157,40 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>94.59999999999999</v>
+        <v>101</v>
       </c>
       <c r="G17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>102.6</v>
+        <v>111</v>
       </c>
       <c r="J17" t="n">
-        <v>102.6</v>
+        <v>111</v>
       </c>
       <c r="K17" t="n">
-        <v>102.6</v>
+        <v>111</v>
       </c>
       <c r="L17" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1199,40 +1199,40 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>93.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>101.4</v>
+        <v>108.1</v>
       </c>
       <c r="J18" t="n">
-        <v>101.4</v>
+        <v>108.1</v>
       </c>
       <c r="K18" t="n">
-        <v>101.4</v>
+        <v>108.1</v>
       </c>
       <c r="L18" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1241,25 +1241,25 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>92.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="G19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>100.4</v>
+        <v>105.7</v>
       </c>
       <c r="J19" t="n">
-        <v>100.4</v>
+        <v>105.7</v>
       </c>
       <c r="K19" t="n">
-        <v>100.4</v>
+        <v>105.7</v>
       </c>
       <c r="L19" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="20">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1283,7 +1283,7 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>91.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G20" t="n">
         <v>8</v>
@@ -1292,13 +1292,13 @@
         <v>4</v>
       </c>
       <c r="I20" t="n">
-        <v>99.8</v>
+        <v>102.6</v>
       </c>
       <c r="J20" t="n">
-        <v>99.8</v>
+        <v>102.6</v>
       </c>
       <c r="K20" t="n">
-        <v>99.8</v>
+        <v>102.6</v>
       </c>
       <c r="L20" t="n">
         <v>122</v>
@@ -1316,7 +1316,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1325,7 +1325,7 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>91.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G21" t="n">
         <v>8</v>
@@ -1334,13 +1334,13 @@
         <v>4</v>
       </c>
       <c r="I21" t="n">
-        <v>99.8</v>
+        <v>101.4</v>
       </c>
       <c r="J21" t="n">
-        <v>99.8</v>
+        <v>101.4</v>
       </c>
       <c r="K21" t="n">
-        <v>99.8</v>
+        <v>101.4</v>
       </c>
       <c r="L21" t="n">
         <v>122</v>
@@ -1354,11 +1354,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1367,7 +1367,7 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>80.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G22" t="n">
         <v>8</v>
@@ -1376,13 +1376,13 @@
         <v>4</v>
       </c>
       <c r="I22" t="n">
-        <v>88.90000000000001</v>
+        <v>100.4</v>
       </c>
       <c r="J22" t="n">
-        <v>88.90000000000001</v>
+        <v>100.4</v>
       </c>
       <c r="K22" t="n">
-        <v>88.90000000000001</v>
+        <v>100.4</v>
       </c>
       <c r="L22" t="n">
         <v>122</v>
@@ -1396,11 +1396,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>79</v>
+        <v>91.8</v>
       </c>
       <c r="G23" t="n">
         <v>8</v>
@@ -1418,13 +1418,13 @@
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>87</v>
+        <v>99.8</v>
       </c>
       <c r="J23" t="n">
-        <v>87</v>
+        <v>99.8</v>
       </c>
       <c r="K23" t="n">
-        <v>87</v>
+        <v>99.8</v>
       </c>
       <c r="L23" t="n">
         <v>122</v>
@@ -1438,11 +1438,11 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>77.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="G24" t="n">
         <v>8</v>
@@ -1460,13 +1460,13 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>85.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="J24" t="n">
-        <v>85.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="K24" t="n">
-        <v>85.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="L24" t="n">
         <v>122</v>
@@ -1480,11 +1480,11 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>74.7</v>
+        <v>91.8</v>
       </c>
       <c r="G25" t="n">
         <v>8</v>
@@ -1502,13 +1502,13 @@
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>82.7</v>
+        <v>99.8</v>
       </c>
       <c r="J25" t="n">
-        <v>82.7</v>
+        <v>99.8</v>
       </c>
       <c r="K25" t="n">
-        <v>82.7</v>
+        <v>99.8</v>
       </c>
       <c r="L25" t="n">
         <v>122</v>
@@ -1526,7 +1526,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>73.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>8</v>
@@ -1544,13 +1544,13 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>81.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>81.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>81.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>122</v>
@@ -1564,11 +1564,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>78.2</v>
+        <v>79</v>
       </c>
       <c r="G27" t="n">
         <v>8</v>
@@ -1586,13 +1586,13 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="J27" t="n">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="K27" t="n">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="L27" t="n">
         <v>122</v>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>73.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G28" t="n">
         <v>8</v>
@@ -1628,13 +1628,13 @@
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>81.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>81.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>81.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L28" t="n">
         <v>122</v>
@@ -1648,11 +1648,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>70.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="G29" t="n">
         <v>8</v>
@@ -1670,13 +1670,13 @@
         <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>78.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="J29" t="n">
-        <v>78.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K29" t="n">
-        <v>78.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="L29" t="n">
         <v>122</v>
@@ -1690,7 +1690,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>67.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="G30" t="n">
         <v>8</v>
@@ -1712,13 +1712,13 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>75.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="J30" t="n">
-        <v>75.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K30" t="n">
-        <v>75.09999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="L30" t="n">
         <v>122</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>65.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="G31" t="n">
         <v>8</v>
@@ -1754,13 +1754,13 @@
         <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>73.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="J31" t="n">
-        <v>73.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K31" t="n">
-        <v>73.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="L31" t="n">
         <v>122</v>
@@ -1769,12 +1769,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1787,36 +1787,36 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>209.5</v>
+        <v>78.2</v>
       </c>
       <c r="G32" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H32" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>231.5</v>
+        <v>86.2</v>
       </c>
       <c r="J32" t="n">
-        <v>231.5</v>
+        <v>86.2</v>
       </c>
       <c r="K32" t="n">
-        <v>231.5</v>
+        <v>86.2</v>
       </c>
       <c r="L32" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1829,36 +1829,36 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>203.3</v>
+        <v>73.5</v>
       </c>
       <c r="G33" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>225.3</v>
+        <v>81.5</v>
       </c>
       <c r="J33" t="n">
-        <v>225.3</v>
+        <v>81.5</v>
       </c>
       <c r="K33" t="n">
-        <v>225.3</v>
+        <v>81.5</v>
       </c>
       <c r="L33" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1871,40 +1871,40 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>198.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H34" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>220.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>220.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>220.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1913,40 +1913,40 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>194.8</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H35" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>216.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>216.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>216.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1955,40 +1955,40 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>194.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H36" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>216.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>216.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>216.7</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1997,25 +1997,25 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>190.2</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H37" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>212.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>212.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>212.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="38">
@@ -2026,11 +2026,11 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D38" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>180.6</v>
+        <v>209.5</v>
       </c>
       <c r="G38" t="n">
         <v>22</v>
@@ -2048,13 +2048,13 @@
         <v>11</v>
       </c>
       <c r="I38" t="n">
-        <v>202.6</v>
+        <v>231.5</v>
       </c>
       <c r="J38" t="n">
-        <v>202.6</v>
+        <v>231.5</v>
       </c>
       <c r="K38" t="n">
-        <v>202.6</v>
+        <v>231.5</v>
       </c>
       <c r="L38" t="n">
         <v>275</v>
@@ -2068,11 +2068,11 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
@@ -2081,7 +2081,7 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>172.2</v>
+        <v>203.3</v>
       </c>
       <c r="G39" t="n">
         <v>22</v>
@@ -2090,13 +2090,13 @@
         <v>11</v>
       </c>
       <c r="I39" t="n">
-        <v>194.2</v>
+        <v>225.3</v>
       </c>
       <c r="J39" t="n">
-        <v>194.2</v>
+        <v>225.3</v>
       </c>
       <c r="K39" t="n">
-        <v>194.2</v>
+        <v>225.3</v>
       </c>
       <c r="L39" t="n">
         <v>275</v>
@@ -2110,11 +2110,11 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D40" t="n">
         <v>0</v>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>161</v>
+        <v>198.2</v>
       </c>
       <c r="G40" t="n">
         <v>22</v>
@@ -2132,13 +2132,13 @@
         <v>11</v>
       </c>
       <c r="I40" t="n">
-        <v>183</v>
+        <v>220.2</v>
       </c>
       <c r="J40" t="n">
-        <v>183</v>
+        <v>220.2</v>
       </c>
       <c r="K40" t="n">
-        <v>183</v>
+        <v>220.2</v>
       </c>
       <c r="L40" t="n">
         <v>275</v>
@@ -2152,11 +2152,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>156.5</v>
+        <v>195</v>
       </c>
       <c r="G41" t="n">
         <v>22</v>
@@ -2174,13 +2174,13 @@
         <v>11</v>
       </c>
       <c r="I41" t="n">
-        <v>178.5</v>
+        <v>217</v>
       </c>
       <c r="J41" t="n">
-        <v>178.5</v>
+        <v>217</v>
       </c>
       <c r="K41" t="n">
-        <v>178.5</v>
+        <v>217</v>
       </c>
       <c r="L41" t="n">
         <v>275</v>
@@ -2194,11 +2194,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D42" t="n">
         <v>0</v>
@@ -2207,7 +2207,7 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>185.2</v>
+        <v>194.8</v>
       </c>
       <c r="G42" t="n">
         <v>22</v>
@@ -2216,13 +2216,13 @@
         <v>11</v>
       </c>
       <c r="I42" t="n">
-        <v>207.2</v>
+        <v>216.8</v>
       </c>
       <c r="J42" t="n">
-        <v>207.2</v>
+        <v>216.8</v>
       </c>
       <c r="K42" t="n">
-        <v>207.2</v>
+        <v>216.8</v>
       </c>
       <c r="L42" t="n">
         <v>275</v>
@@ -2236,11 +2236,11 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>172.9</v>
+        <v>194.7</v>
       </c>
       <c r="G43" t="n">
         <v>22</v>
@@ -2258,13 +2258,13 @@
         <v>11</v>
       </c>
       <c r="I43" t="n">
-        <v>194.9</v>
+        <v>216.7</v>
       </c>
       <c r="J43" t="n">
-        <v>194.9</v>
+        <v>216.7</v>
       </c>
       <c r="K43" t="n">
-        <v>194.9</v>
+        <v>216.7</v>
       </c>
       <c r="L43" t="n">
         <v>275</v>
@@ -2278,11 +2278,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>162</v>
+        <v>190.2</v>
       </c>
       <c r="G44" t="n">
         <v>22</v>
@@ -2300,13 +2300,13 @@
         <v>11</v>
       </c>
       <c r="I44" t="n">
-        <v>184</v>
+        <v>212.2</v>
       </c>
       <c r="J44" t="n">
-        <v>184</v>
+        <v>212.2</v>
       </c>
       <c r="K44" t="n">
-        <v>184</v>
+        <v>212.2</v>
       </c>
       <c r="L44" t="n">
         <v>275</v>
@@ -2320,11 +2320,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>148.9</v>
+        <v>180.6</v>
       </c>
       <c r="G45" t="n">
         <v>22</v>
@@ -2342,13 +2342,13 @@
         <v>11</v>
       </c>
       <c r="I45" t="n">
-        <v>170.9</v>
+        <v>202.6</v>
       </c>
       <c r="J45" t="n">
-        <v>170.9</v>
+        <v>202.6</v>
       </c>
       <c r="K45" t="n">
-        <v>170.9</v>
+        <v>202.6</v>
       </c>
       <c r="L45" t="n">
         <v>275</v>
@@ -2362,11 +2362,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>143.4</v>
+        <v>172.2</v>
       </c>
       <c r="G46" t="n">
         <v>22</v>
@@ -2384,13 +2384,13 @@
         <v>11</v>
       </c>
       <c r="I46" t="n">
-        <v>165.4</v>
+        <v>194.2</v>
       </c>
       <c r="J46" t="n">
-        <v>165.4</v>
+        <v>194.2</v>
       </c>
       <c r="K46" t="n">
-        <v>165.4</v>
+        <v>194.2</v>
       </c>
       <c r="L46" t="n">
         <v>275</v>
@@ -2399,16 +2399,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>243.9</v>
+        <v>165.7</v>
       </c>
       <c r="G47" t="n">
         <v>22</v>
@@ -2426,31 +2426,31 @@
         <v>11</v>
       </c>
       <c r="I47" t="n">
-        <v>265.9</v>
+        <v>187.7</v>
       </c>
       <c r="J47" t="n">
-        <v>265.9</v>
+        <v>187.7</v>
       </c>
       <c r="K47" t="n">
-        <v>265.9</v>
+        <v>187.7</v>
       </c>
       <c r="L47" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>234.5</v>
+        <v>161</v>
       </c>
       <c r="G48" t="n">
         <v>22</v>
@@ -2468,31 +2468,31 @@
         <v>11</v>
       </c>
       <c r="I48" t="n">
-        <v>256.5</v>
+        <v>183</v>
       </c>
       <c r="J48" t="n">
-        <v>256.5</v>
+        <v>183</v>
       </c>
       <c r="K48" t="n">
-        <v>256.5</v>
+        <v>183</v>
       </c>
       <c r="L48" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>226.1</v>
+        <v>156.5</v>
       </c>
       <c r="G49" t="n">
         <v>22</v>
@@ -2510,31 +2510,31 @@
         <v>11</v>
       </c>
       <c r="I49" t="n">
-        <v>248.1</v>
+        <v>178.5</v>
       </c>
       <c r="J49" t="n">
-        <v>248.1</v>
+        <v>178.5</v>
       </c>
       <c r="K49" t="n">
-        <v>248.1</v>
+        <v>178.5</v>
       </c>
       <c r="L49" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>219.5</v>
+        <v>185.2</v>
       </c>
       <c r="G50" t="n">
         <v>22</v>
@@ -2552,31 +2552,31 @@
         <v>11</v>
       </c>
       <c r="I50" t="n">
-        <v>241.5</v>
+        <v>207.2</v>
       </c>
       <c r="J50" t="n">
-        <v>241.5</v>
+        <v>207.2</v>
       </c>
       <c r="K50" t="n">
-        <v>241.5</v>
+        <v>207.2</v>
       </c>
       <c r="L50" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>219.5</v>
+        <v>172.9</v>
       </c>
       <c r="G51" t="n">
         <v>22</v>
@@ -2594,31 +2594,31 @@
         <v>11</v>
       </c>
       <c r="I51" t="n">
-        <v>241.5</v>
+        <v>194.9</v>
       </c>
       <c r="J51" t="n">
-        <v>241.5</v>
+        <v>194.9</v>
       </c>
       <c r="K51" t="n">
-        <v>241.5</v>
+        <v>194.9</v>
       </c>
       <c r="L51" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>224.5</v>
+        <v>162</v>
       </c>
       <c r="G52" t="n">
         <v>22</v>
@@ -2636,31 +2636,31 @@
         <v>11</v>
       </c>
       <c r="I52" t="n">
-        <v>246.5</v>
+        <v>184</v>
       </c>
       <c r="J52" t="n">
-        <v>246.5</v>
+        <v>184</v>
       </c>
       <c r="K52" t="n">
-        <v>246.5</v>
+        <v>184</v>
       </c>
       <c r="L52" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>211.7</v>
+        <v>153.5</v>
       </c>
       <c r="G53" t="n">
         <v>22</v>
@@ -2678,31 +2678,31 @@
         <v>11</v>
       </c>
       <c r="I53" t="n">
-        <v>233.7</v>
+        <v>175.5</v>
       </c>
       <c r="J53" t="n">
-        <v>233.7</v>
+        <v>175.5</v>
       </c>
       <c r="K53" t="n">
-        <v>233.7</v>
+        <v>175.5</v>
       </c>
       <c r="L53" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>199.8</v>
+        <v>148.9</v>
       </c>
       <c r="G54" t="n">
         <v>22</v>
@@ -2720,31 +2720,31 @@
         <v>11</v>
       </c>
       <c r="I54" t="n">
-        <v>221.8</v>
+        <v>170.9</v>
       </c>
       <c r="J54" t="n">
-        <v>221.8</v>
+        <v>170.9</v>
       </c>
       <c r="K54" t="n">
-        <v>221.8</v>
+        <v>170.9</v>
       </c>
       <c r="L54" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>183.5</v>
+        <v>143.4</v>
       </c>
       <c r="G55" t="n">
         <v>22</v>
@@ -2762,16 +2762,16 @@
         <v>11</v>
       </c>
       <c r="I55" t="n">
-        <v>205.5</v>
+        <v>165.4</v>
       </c>
       <c r="J55" t="n">
-        <v>205.5</v>
+        <v>165.4</v>
       </c>
       <c r="K55" t="n">
-        <v>205.5</v>
+        <v>165.4</v>
       </c>
       <c r="L55" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="56">
@@ -2782,11 +2782,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>176.1</v>
+        <v>243.9</v>
       </c>
       <c r="G56" t="n">
         <v>22</v>
@@ -2804,13 +2804,13 @@
         <v>11</v>
       </c>
       <c r="I56" t="n">
-        <v>198.1</v>
+        <v>265.9</v>
       </c>
       <c r="J56" t="n">
-        <v>198.1</v>
+        <v>265.9</v>
       </c>
       <c r="K56" t="n">
-        <v>198.1</v>
+        <v>265.9</v>
       </c>
       <c r="L56" t="n">
         <v>318</v>
@@ -2824,11 +2824,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>220</v>
+        <v>234.5</v>
       </c>
       <c r="G57" t="n">
         <v>22</v>
@@ -2846,13 +2846,13 @@
         <v>11</v>
       </c>
       <c r="I57" t="n">
-        <v>242</v>
+        <v>256.5</v>
       </c>
       <c r="J57" t="n">
-        <v>242</v>
+        <v>256.5</v>
       </c>
       <c r="K57" t="n">
-        <v>242</v>
+        <v>256.5</v>
       </c>
       <c r="L57" t="n">
         <v>318</v>
@@ -2866,11 +2866,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>204.1</v>
+        <v>226.1</v>
       </c>
       <c r="G58" t="n">
         <v>22</v>
@@ -2888,13 +2888,13 @@
         <v>11</v>
       </c>
       <c r="I58" t="n">
-        <v>226.1</v>
+        <v>248.1</v>
       </c>
       <c r="J58" t="n">
-        <v>226.1</v>
+        <v>248.1</v>
       </c>
       <c r="K58" t="n">
-        <v>226.1</v>
+        <v>248.1</v>
       </c>
       <c r="L58" t="n">
         <v>318</v>
@@ -2908,11 +2908,11 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>189.5</v>
+        <v>219.8</v>
       </c>
       <c r="G59" t="n">
         <v>22</v>
@@ -2930,13 +2930,13 @@
         <v>11</v>
       </c>
       <c r="I59" t="n">
-        <v>211.5</v>
+        <v>241.8</v>
       </c>
       <c r="J59" t="n">
-        <v>211.5</v>
+        <v>241.8</v>
       </c>
       <c r="K59" t="n">
-        <v>211.5</v>
+        <v>241.8</v>
       </c>
       <c r="L59" t="n">
         <v>318</v>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>171.5</v>
+        <v>219.5</v>
       </c>
       <c r="G60" t="n">
         <v>22</v>
@@ -2972,13 +2972,13 @@
         <v>11</v>
       </c>
       <c r="I60" t="n">
-        <v>193.5</v>
+        <v>241.5</v>
       </c>
       <c r="J60" t="n">
-        <v>193.5</v>
+        <v>241.5</v>
       </c>
       <c r="K60" t="n">
-        <v>193.5</v>
+        <v>241.5</v>
       </c>
       <c r="L60" t="n">
         <v>318</v>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>162.9</v>
+        <v>219.5</v>
       </c>
       <c r="G61" t="n">
         <v>22</v>
@@ -3014,20 +3014,524 @@
         <v>11</v>
       </c>
       <c r="I61" t="n">
-        <v>184.9</v>
+        <v>241.5</v>
       </c>
       <c r="J61" t="n">
-        <v>184.9</v>
+        <v>241.5</v>
       </c>
       <c r="K61" t="n">
-        <v>184.9</v>
+        <v>241.5</v>
       </c>
       <c r="L61" t="n">
         <v>318</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>160</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" t="n">
+        <v>224.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>22</v>
+      </c>
+      <c r="H62" t="n">
+        <v>11</v>
+      </c>
+      <c r="I62" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="K62" t="n">
+        <v>246.5</v>
+      </c>
+      <c r="L62" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>177</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="G63" t="n">
+        <v>22</v>
+      </c>
+      <c r="H63" t="n">
+        <v>11</v>
+      </c>
+      <c r="I63" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="J63" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="K63" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="L63" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>201</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="G64" t="n">
+        <v>22</v>
+      </c>
+      <c r="H64" t="n">
+        <v>11</v>
+      </c>
+      <c r="I64" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="J64" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="K64" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="L64" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>241</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="G65" t="n">
+        <v>22</v>
+      </c>
+      <c r="H65" t="n">
+        <v>11</v>
+      </c>
+      <c r="I65" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="J65" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="K65" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="L65" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>250</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>22</v>
+      </c>
+      <c r="H66" t="n">
+        <v>11</v>
+      </c>
+      <c r="I66" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="J66" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="L66" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>300</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="G67" t="n">
+        <v>22</v>
+      </c>
+      <c r="H67" t="n">
+        <v>11</v>
+      </c>
+      <c r="I67" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="J67" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="L67" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>160</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" t="n">
+        <v>220</v>
+      </c>
+      <c r="G68" t="n">
+        <v>22</v>
+      </c>
+      <c r="H68" t="n">
+        <v>11</v>
+      </c>
+      <c r="I68" t="n">
+        <v>242</v>
+      </c>
+      <c r="J68" t="n">
+        <v>242</v>
+      </c>
+      <c r="K68" t="n">
+        <v>242</v>
+      </c>
+      <c r="L68" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>177</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" t="n">
+        <v>204.1</v>
+      </c>
+      <c r="G69" t="n">
+        <v>22</v>
+      </c>
+      <c r="H69" t="n">
+        <v>11</v>
+      </c>
+      <c r="I69" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="J69" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="L69" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>201</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="G70" t="n">
+        <v>22</v>
+      </c>
+      <c r="H70" t="n">
+        <v>11</v>
+      </c>
+      <c r="I70" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="J70" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="K70" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="L70" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>241</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="G71" t="n">
+        <v>22</v>
+      </c>
+      <c r="H71" t="n">
+        <v>11</v>
+      </c>
+      <c r="I71" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="J71" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="K71" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="L71" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>250</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="G72" t="n">
+        <v>22</v>
+      </c>
+      <c r="H72" t="n">
+        <v>11</v>
+      </c>
+      <c r="I72" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="J72" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="K72" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="L72" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>300</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0</v>
+      </c>
+      <c r="F73" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="G73" t="n">
+        <v>22</v>
+      </c>
+      <c r="H73" t="n">
+        <v>11</v>
+      </c>
+      <c r="I73" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="J73" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="K73" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="L73" t="n">
+        <v>318</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L61"/>
+  <autoFilter ref="A1:L73"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/livrables/temps_scenario_2.xlsx
+++ b/livrables/temps_scenario_2.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="temps_scenario_2" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'temps_scenario_2'!$A$1:$L$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'temps_scenario_2'!$A$1:$L$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L73"/>
+  <dimension ref="A1:L85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -518,7 +518,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -527,7 +527,7 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>138.1</v>
+        <v>139.8</v>
       </c>
       <c r="G2" t="n">
         <v>10</v>
@@ -536,13 +536,13 @@
         <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>148.1</v>
+        <v>149.8</v>
       </c>
       <c r="J2" t="n">
-        <v>148.1</v>
+        <v>149.8</v>
       </c>
       <c r="K2" t="n">
-        <v>148.1</v>
+        <v>149.8</v>
       </c>
       <c r="L2" t="n">
         <v>202.5</v>
@@ -560,7 +560,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -569,7 +569,7 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>135.4</v>
+        <v>138.1</v>
       </c>
       <c r="G3" t="n">
         <v>10</v>
@@ -578,13 +578,13 @@
         <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>145.4</v>
+        <v>148.1</v>
       </c>
       <c r="J3" t="n">
-        <v>145.4</v>
+        <v>148.1</v>
       </c>
       <c r="K3" t="n">
-        <v>145.4</v>
+        <v>148.1</v>
       </c>
       <c r="L3" t="n">
         <v>202.5</v>
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -611,7 +611,7 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>133.4</v>
+        <v>135.4</v>
       </c>
       <c r="G4" t="n">
         <v>10</v>
@@ -620,13 +620,13 @@
         <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>143.4</v>
+        <v>145.4</v>
       </c>
       <c r="J4" t="n">
-        <v>143.4</v>
+        <v>145.4</v>
       </c>
       <c r="K4" t="n">
-        <v>143.4</v>
+        <v>145.4</v>
       </c>
       <c r="L4" t="n">
         <v>202.5</v>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -653,7 +653,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>132.6</v>
+        <v>133.4</v>
       </c>
       <c r="G5" t="n">
         <v>10</v>
@@ -662,13 +662,13 @@
         <v>5</v>
       </c>
       <c r="I5" t="n">
-        <v>142.6</v>
+        <v>143.4</v>
       </c>
       <c r="J5" t="n">
-        <v>142.6</v>
+        <v>143.4</v>
       </c>
       <c r="K5" t="n">
-        <v>142.6</v>
+        <v>143.4</v>
       </c>
       <c r="L5" t="n">
         <v>202.5</v>
@@ -686,7 +686,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -766,11 +766,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -779,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>121.5</v>
+        <v>132.6</v>
       </c>
       <c r="G8" t="n">
         <v>10</v>
@@ -788,13 +788,13 @@
         <v>5</v>
       </c>
       <c r="I8" t="n">
-        <v>131.5</v>
+        <v>142.6</v>
       </c>
       <c r="J8" t="n">
-        <v>131.5</v>
+        <v>142.6</v>
       </c>
       <c r="K8" t="n">
-        <v>131.5</v>
+        <v>142.6</v>
       </c>
       <c r="L8" t="n">
         <v>202.5</v>
@@ -812,7 +812,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>117.2</v>
+        <v>124.2</v>
       </c>
       <c r="G9" t="n">
         <v>10</v>
@@ -830,13 +830,13 @@
         <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>127.2</v>
+        <v>134.2</v>
       </c>
       <c r="J9" t="n">
-        <v>127.2</v>
+        <v>134.2</v>
       </c>
       <c r="K9" t="n">
-        <v>127.2</v>
+        <v>134.2</v>
       </c>
       <c r="L9" t="n">
         <v>202.5</v>
@@ -854,7 +854,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
@@ -863,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>113.4</v>
+        <v>121.5</v>
       </c>
       <c r="G10" t="n">
         <v>10</v>
@@ -872,13 +872,13 @@
         <v>5</v>
       </c>
       <c r="I10" t="n">
-        <v>123.4</v>
+        <v>131.5</v>
       </c>
       <c r="J10" t="n">
-        <v>123.4</v>
+        <v>131.5</v>
       </c>
       <c r="K10" t="n">
-        <v>123.4</v>
+        <v>131.5</v>
       </c>
       <c r="L10" t="n">
         <v>202.5</v>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>110.9</v>
+        <v>117.2</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
@@ -914,13 +914,13 @@
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>120.9</v>
+        <v>127.2</v>
       </c>
       <c r="J11" t="n">
-        <v>120.9</v>
+        <v>127.2</v>
       </c>
       <c r="K11" t="n">
-        <v>120.9</v>
+        <v>127.2</v>
       </c>
       <c r="L11" t="n">
         <v>202.5</v>
@@ -938,7 +938,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -947,7 +947,7 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>107.8</v>
+        <v>113.4</v>
       </c>
       <c r="G12" t="n">
         <v>10</v>
@@ -956,13 +956,13 @@
         <v>5</v>
       </c>
       <c r="I12" t="n">
-        <v>117.8</v>
+        <v>123.4</v>
       </c>
       <c r="J12" t="n">
-        <v>117.8</v>
+        <v>123.4</v>
       </c>
       <c r="K12" t="n">
-        <v>117.8</v>
+        <v>123.4</v>
       </c>
       <c r="L12" t="n">
         <v>202.5</v>
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>106</v>
+        <v>110.9</v>
       </c>
       <c r="G13" t="n">
         <v>10</v>
@@ -998,13 +998,13 @@
         <v>5</v>
       </c>
       <c r="I13" t="n">
-        <v>116</v>
+        <v>120.9</v>
       </c>
       <c r="J13" t="n">
-        <v>116</v>
+        <v>120.9</v>
       </c>
       <c r="K13" t="n">
-        <v>116</v>
+        <v>120.9</v>
       </c>
       <c r="L13" t="n">
         <v>202.5</v>
@@ -1018,11 +1018,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>116.1</v>
+        <v>107.8</v>
       </c>
       <c r="G14" t="n">
         <v>10</v>
@@ -1040,13 +1040,13 @@
         <v>5</v>
       </c>
       <c r="I14" t="n">
-        <v>126.1</v>
+        <v>117.8</v>
       </c>
       <c r="J14" t="n">
-        <v>126.1</v>
+        <v>117.8</v>
       </c>
       <c r="K14" t="n">
-        <v>126.1</v>
+        <v>117.8</v>
       </c>
       <c r="L14" t="n">
         <v>202.5</v>
@@ -1060,11 +1060,11 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1073,7 +1073,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>109.7</v>
+        <v>106</v>
       </c>
       <c r="G15" t="n">
         <v>10</v>
@@ -1082,13 +1082,13 @@
         <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>119.7</v>
+        <v>116</v>
       </c>
       <c r="J15" t="n">
-        <v>119.7</v>
+        <v>116</v>
       </c>
       <c r="K15" t="n">
-        <v>119.7</v>
+        <v>116</v>
       </c>
       <c r="L15" t="n">
         <v>202.5</v>
@@ -1106,7 +1106,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -1115,7 +1115,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>104.6</v>
+        <v>119.4</v>
       </c>
       <c r="G16" t="n">
         <v>10</v>
@@ -1124,13 +1124,13 @@
         <v>5</v>
       </c>
       <c r="I16" t="n">
-        <v>114.6</v>
+        <v>129.4</v>
       </c>
       <c r="J16" t="n">
-        <v>114.6</v>
+        <v>129.4</v>
       </c>
       <c r="K16" t="n">
-        <v>114.6</v>
+        <v>129.4</v>
       </c>
       <c r="L16" t="n">
         <v>202.5</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>101</v>
+        <v>116.1</v>
       </c>
       <c r="G17" t="n">
         <v>10</v>
@@ -1166,13 +1166,13 @@
         <v>5</v>
       </c>
       <c r="I17" t="n">
-        <v>111</v>
+        <v>126.1</v>
       </c>
       <c r="J17" t="n">
-        <v>111</v>
+        <v>126.1</v>
       </c>
       <c r="K17" t="n">
-        <v>111</v>
+        <v>126.1</v>
       </c>
       <c r="L17" t="n">
         <v>202.5</v>
@@ -1190,7 +1190,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -1199,7 +1199,7 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>98.09999999999999</v>
+        <v>109.7</v>
       </c>
       <c r="G18" t="n">
         <v>10</v>
@@ -1208,13 +1208,13 @@
         <v>5</v>
       </c>
       <c r="I18" t="n">
-        <v>108.1</v>
+        <v>119.7</v>
       </c>
       <c r="J18" t="n">
-        <v>108.1</v>
+        <v>119.7</v>
       </c>
       <c r="K18" t="n">
-        <v>108.1</v>
+        <v>119.7</v>
       </c>
       <c r="L18" t="n">
         <v>202.5</v>
@@ -1232,7 +1232,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>95.7</v>
+        <v>104.6</v>
       </c>
       <c r="G19" t="n">
         <v>10</v>
@@ -1250,13 +1250,13 @@
         <v>5</v>
       </c>
       <c r="I19" t="n">
-        <v>105.7</v>
+        <v>114.6</v>
       </c>
       <c r="J19" t="n">
-        <v>105.7</v>
+        <v>114.6</v>
       </c>
       <c r="K19" t="n">
-        <v>105.7</v>
+        <v>114.6</v>
       </c>
       <c r="L19" t="n">
         <v>202.5</v>
@@ -1265,16 +1265,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -1283,40 +1283,40 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>94.59999999999999</v>
+        <v>101</v>
       </c>
       <c r="G20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" t="n">
-        <v>102.6</v>
+        <v>111</v>
       </c>
       <c r="J20" t="n">
-        <v>102.6</v>
+        <v>111</v>
       </c>
       <c r="K20" t="n">
-        <v>102.6</v>
+        <v>111</v>
       </c>
       <c r="L20" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -1325,40 +1325,40 @@
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>93.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="G21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" t="n">
-        <v>101.4</v>
+        <v>108.1</v>
       </c>
       <c r="J21" t="n">
-        <v>101.4</v>
+        <v>108.1</v>
       </c>
       <c r="K21" t="n">
-        <v>101.4</v>
+        <v>108.1</v>
       </c>
       <c r="L21" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MTL-Ott</t>
+          <t>MTL-QC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -1367,25 +1367,25 @@
         <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>92.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="G22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>100.4</v>
+        <v>105.7</v>
       </c>
       <c r="J22" t="n">
-        <v>100.4</v>
+        <v>105.7</v>
       </c>
       <c r="K22" t="n">
-        <v>100.4</v>
+        <v>105.7</v>
       </c>
       <c r="L22" t="n">
-        <v>122</v>
+        <v>202.5</v>
       </c>
     </row>
     <row r="23">
@@ -1400,7 +1400,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="D23" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>91.8</v>
+        <v>95.3</v>
       </c>
       <c r="G23" t="n">
         <v>8</v>
@@ -1418,13 +1418,13 @@
         <v>4</v>
       </c>
       <c r="I23" t="n">
-        <v>99.8</v>
+        <v>103.3</v>
       </c>
       <c r="J23" t="n">
-        <v>99.8</v>
+        <v>103.3</v>
       </c>
       <c r="K23" t="n">
-        <v>99.8</v>
+        <v>103.3</v>
       </c>
       <c r="L23" t="n">
         <v>122</v>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -1451,7 +1451,7 @@
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>91.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>8</v>
@@ -1460,13 +1460,13 @@
         <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>99.8</v>
+        <v>102.6</v>
       </c>
       <c r="J24" t="n">
-        <v>99.8</v>
+        <v>102.6</v>
       </c>
       <c r="K24" t="n">
-        <v>99.8</v>
+        <v>102.6</v>
       </c>
       <c r="L24" t="n">
         <v>122</v>
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
@@ -1493,7 +1493,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>91.8</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>8</v>
@@ -1502,13 +1502,13 @@
         <v>4</v>
       </c>
       <c r="I25" t="n">
-        <v>99.8</v>
+        <v>101.4</v>
       </c>
       <c r="J25" t="n">
-        <v>99.8</v>
+        <v>101.4</v>
       </c>
       <c r="K25" t="n">
-        <v>99.8</v>
+        <v>101.4</v>
       </c>
       <c r="L25" t="n">
         <v>122</v>
@@ -1522,11 +1522,11 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1535,7 +1535,7 @@
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>80.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="G26" t="n">
         <v>8</v>
@@ -1544,13 +1544,13 @@
         <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>88.90000000000001</v>
+        <v>100.4</v>
       </c>
       <c r="J26" t="n">
-        <v>88.90000000000001</v>
+        <v>100.4</v>
       </c>
       <c r="K26" t="n">
-        <v>88.90000000000001</v>
+        <v>100.4</v>
       </c>
       <c r="L26" t="n">
         <v>122</v>
@@ -1564,11 +1564,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="D27" t="n">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>79</v>
+        <v>91.8</v>
       </c>
       <c r="G27" t="n">
         <v>8</v>
@@ -1586,13 +1586,13 @@
         <v>4</v>
       </c>
       <c r="I27" t="n">
-        <v>87</v>
+        <v>99.8</v>
       </c>
       <c r="J27" t="n">
-        <v>87</v>
+        <v>99.8</v>
       </c>
       <c r="K27" t="n">
-        <v>87</v>
+        <v>99.8</v>
       </c>
       <c r="L27" t="n">
         <v>122</v>
@@ -1606,11 +1606,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>77.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="G28" t="n">
         <v>8</v>
@@ -1628,13 +1628,13 @@
         <v>4</v>
       </c>
       <c r="I28" t="n">
-        <v>85.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="J28" t="n">
-        <v>85.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="K28" t="n">
-        <v>85.40000000000001</v>
+        <v>99.8</v>
       </c>
       <c r="L28" t="n">
         <v>122</v>
@@ -1648,11 +1648,11 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1661,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>76.2</v>
+        <v>91.8</v>
       </c>
       <c r="G29" t="n">
         <v>8</v>
@@ -1670,13 +1670,13 @@
         <v>4</v>
       </c>
       <c r="I29" t="n">
-        <v>84.2</v>
+        <v>99.8</v>
       </c>
       <c r="J29" t="n">
-        <v>84.2</v>
+        <v>99.8</v>
       </c>
       <c r="K29" t="n">
-        <v>84.2</v>
+        <v>99.8</v>
       </c>
       <c r="L29" t="n">
         <v>122</v>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>74.7</v>
+        <v>83</v>
       </c>
       <c r="G30" t="n">
         <v>8</v>
@@ -1712,13 +1712,13 @@
         <v>4</v>
       </c>
       <c r="I30" t="n">
-        <v>82.7</v>
+        <v>91</v>
       </c>
       <c r="J30" t="n">
-        <v>82.7</v>
+        <v>91</v>
       </c>
       <c r="K30" t="n">
-        <v>82.7</v>
+        <v>91</v>
       </c>
       <c r="L30" t="n">
         <v>122</v>
@@ -1736,7 +1736,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D31" t="n">
         <v>0</v>
@@ -1745,7 +1745,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>73.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="G31" t="n">
         <v>8</v>
@@ -1754,13 +1754,13 @@
         <v>4</v>
       </c>
       <c r="I31" t="n">
-        <v>81.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>81.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>81.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="L31" t="n">
         <v>122</v>
@@ -1774,11 +1774,11 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1787,7 +1787,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>78.2</v>
+        <v>79</v>
       </c>
       <c r="G32" t="n">
         <v>8</v>
@@ -1796,13 +1796,13 @@
         <v>4</v>
       </c>
       <c r="I32" t="n">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="J32" t="n">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="K32" t="n">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="L32" t="n">
         <v>122</v>
@@ -1816,11 +1816,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>73.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G33" t="n">
         <v>8</v>
@@ -1838,13 +1838,13 @@
         <v>4</v>
       </c>
       <c r="I33" t="n">
-        <v>81.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>81.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>81.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L33" t="n">
         <v>122</v>
@@ -1858,11 +1858,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>201</v>
+        <v>241</v>
       </c>
       <c r="D34" t="n">
         <v>0</v>
@@ -1871,7 +1871,7 @@
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>70.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="G34" t="n">
         <v>8</v>
@@ -1880,13 +1880,13 @@
         <v>4</v>
       </c>
       <c r="I34" t="n">
-        <v>78.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="J34" t="n">
-        <v>78.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="K34" t="n">
-        <v>78.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="L34" t="n">
         <v>122</v>
@@ -1900,11 +1900,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -1913,7 +1913,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>68.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="G35" t="n">
         <v>8</v>
@@ -1922,13 +1922,13 @@
         <v>4</v>
       </c>
       <c r="I35" t="n">
-        <v>76.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="J35" t="n">
-        <v>76.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K35" t="n">
-        <v>76.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="L35" t="n">
         <v>122</v>
@@ -1942,11 +1942,11 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>67.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="G36" t="n">
         <v>8</v>
@@ -1964,13 +1964,13 @@
         <v>4</v>
       </c>
       <c r="I36" t="n">
-        <v>75.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="J36" t="n">
-        <v>75.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="K36" t="n">
-        <v>75.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="L36" t="n">
         <v>122</v>
@@ -1988,7 +1988,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>300</v>
+        <v>153</v>
       </c>
       <c r="D37" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>65.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="G37" t="n">
         <v>8</v>
@@ -2006,13 +2006,13 @@
         <v>4</v>
       </c>
       <c r="I37" t="n">
-        <v>73.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="J37" t="n">
-        <v>73.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="K37" t="n">
-        <v>73.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="L37" t="n">
         <v>122</v>
@@ -2021,12 +2021,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -2039,36 +2039,36 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>209.5</v>
+        <v>78.2</v>
       </c>
       <c r="G38" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H38" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I38" t="n">
-        <v>231.5</v>
+        <v>86.2</v>
       </c>
       <c r="J38" t="n">
-        <v>231.5</v>
+        <v>86.2</v>
       </c>
       <c r="K38" t="n">
-        <v>231.5</v>
+        <v>86.2</v>
       </c>
       <c r="L38" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -2081,36 +2081,36 @@
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>203.3</v>
+        <v>73.5</v>
       </c>
       <c r="G39" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H39" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I39" t="n">
-        <v>225.3</v>
+        <v>81.5</v>
       </c>
       <c r="J39" t="n">
-        <v>225.3</v>
+        <v>81.5</v>
       </c>
       <c r="K39" t="n">
-        <v>225.3</v>
+        <v>81.5</v>
       </c>
       <c r="L39" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -2123,36 +2123,36 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>198.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G40" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H40" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I40" t="n">
-        <v>220.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>220.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>220.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -2165,36 +2165,36 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>195</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H41" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I41" t="n">
-        <v>217</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>217</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>217</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2207,36 +2207,36 @@
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>194.8</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H42" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I42" t="n">
-        <v>216.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>216.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>216.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ott-TO</t>
+          <t>MTL-Ott</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2249,25 +2249,25 @@
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>194.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="G43" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="H43" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>216.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>216.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>216.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>275</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44">
@@ -2278,11 +2278,11 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -2291,7 +2291,7 @@
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>190.2</v>
+        <v>213.1</v>
       </c>
       <c r="G44" t="n">
         <v>22</v>
@@ -2300,13 +2300,13 @@
         <v>11</v>
       </c>
       <c r="I44" t="n">
-        <v>212.2</v>
+        <v>235.1</v>
       </c>
       <c r="J44" t="n">
-        <v>212.2</v>
+        <v>235.1</v>
       </c>
       <c r="K44" t="n">
-        <v>212.2</v>
+        <v>235.1</v>
       </c>
       <c r="L44" t="n">
         <v>275</v>
@@ -2320,11 +2320,11 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -2333,7 +2333,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>180.6</v>
+        <v>209.5</v>
       </c>
       <c r="G45" t="n">
         <v>22</v>
@@ -2342,13 +2342,13 @@
         <v>11</v>
       </c>
       <c r="I45" t="n">
-        <v>202.6</v>
+        <v>231.5</v>
       </c>
       <c r="J45" t="n">
-        <v>202.6</v>
+        <v>231.5</v>
       </c>
       <c r="K45" t="n">
-        <v>202.6</v>
+        <v>231.5</v>
       </c>
       <c r="L45" t="n">
         <v>275</v>
@@ -2362,11 +2362,11 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>201</v>
+        <v>177</v>
       </c>
       <c r="D46" t="n">
         <v>0</v>
@@ -2375,7 +2375,7 @@
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>172.2</v>
+        <v>203.3</v>
       </c>
       <c r="G46" t="n">
         <v>22</v>
@@ -2384,13 +2384,13 @@
         <v>11</v>
       </c>
       <c r="I46" t="n">
-        <v>194.2</v>
+        <v>225.3</v>
       </c>
       <c r="J46" t="n">
-        <v>194.2</v>
+        <v>225.3</v>
       </c>
       <c r="K46" t="n">
-        <v>194.2</v>
+        <v>225.3</v>
       </c>
       <c r="L46" t="n">
         <v>275</v>
@@ -2404,11 +2404,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -2417,7 +2417,7 @@
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>165.7</v>
+        <v>198.2</v>
       </c>
       <c r="G47" t="n">
         <v>22</v>
@@ -2426,13 +2426,13 @@
         <v>11</v>
       </c>
       <c r="I47" t="n">
-        <v>187.7</v>
+        <v>220.2</v>
       </c>
       <c r="J47" t="n">
-        <v>187.7</v>
+        <v>220.2</v>
       </c>
       <c r="K47" t="n">
-        <v>187.7</v>
+        <v>220.2</v>
       </c>
       <c r="L47" t="n">
         <v>275</v>
@@ -2446,11 +2446,11 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -2459,7 +2459,7 @@
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="G48" t="n">
         <v>22</v>
@@ -2468,13 +2468,13 @@
         <v>11</v>
       </c>
       <c r="I48" t="n">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="J48" t="n">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="K48" t="n">
-        <v>183</v>
+        <v>217</v>
       </c>
       <c r="L48" t="n">
         <v>275</v>
@@ -2488,11 +2488,11 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>156.5</v>
+        <v>194.8</v>
       </c>
       <c r="G49" t="n">
         <v>22</v>
@@ -2510,13 +2510,13 @@
         <v>11</v>
       </c>
       <c r="I49" t="n">
-        <v>178.5</v>
+        <v>216.8</v>
       </c>
       <c r="J49" t="n">
-        <v>178.5</v>
+        <v>216.8</v>
       </c>
       <c r="K49" t="n">
-        <v>178.5</v>
+        <v>216.8</v>
       </c>
       <c r="L49" t="n">
         <v>275</v>
@@ -2530,11 +2530,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>160</v>
+        <v>300</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>185.2</v>
+        <v>194.7</v>
       </c>
       <c r="G50" t="n">
         <v>22</v>
@@ -2552,13 +2552,13 @@
         <v>11</v>
       </c>
       <c r="I50" t="n">
-        <v>207.2</v>
+        <v>216.7</v>
       </c>
       <c r="J50" t="n">
-        <v>207.2</v>
+        <v>216.7</v>
       </c>
       <c r="K50" t="n">
-        <v>207.2</v>
+        <v>216.7</v>
       </c>
       <c r="L50" t="n">
         <v>275</v>
@@ -2572,11 +2572,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2585,7 +2585,7 @@
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>172.9</v>
+        <v>195.4</v>
       </c>
       <c r="G51" t="n">
         <v>22</v>
@@ -2594,13 +2594,13 @@
         <v>11</v>
       </c>
       <c r="I51" t="n">
-        <v>194.9</v>
+        <v>217.4</v>
       </c>
       <c r="J51" t="n">
-        <v>194.9</v>
+        <v>217.4</v>
       </c>
       <c r="K51" t="n">
-        <v>194.9</v>
+        <v>217.4</v>
       </c>
       <c r="L51" t="n">
         <v>275</v>
@@ -2614,11 +2614,11 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="D52" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>162</v>
+        <v>190.2</v>
       </c>
       <c r="G52" t="n">
         <v>22</v>
@@ -2636,13 +2636,13 @@
         <v>11</v>
       </c>
       <c r="I52" t="n">
-        <v>184</v>
+        <v>212.2</v>
       </c>
       <c r="J52" t="n">
-        <v>184</v>
+        <v>212.2</v>
       </c>
       <c r="K52" t="n">
-        <v>184</v>
+        <v>212.2</v>
       </c>
       <c r="L52" t="n">
         <v>275</v>
@@ -2656,11 +2656,11 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="D53" t="n">
         <v>0</v>
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>153.5</v>
+        <v>180.6</v>
       </c>
       <c r="G53" t="n">
         <v>22</v>
@@ -2678,13 +2678,13 @@
         <v>11</v>
       </c>
       <c r="I53" t="n">
-        <v>175.5</v>
+        <v>202.6</v>
       </c>
       <c r="J53" t="n">
-        <v>175.5</v>
+        <v>202.6</v>
       </c>
       <c r="K53" t="n">
-        <v>175.5</v>
+        <v>202.6</v>
       </c>
       <c r="L53" t="n">
         <v>275</v>
@@ -2698,11 +2698,11 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>250</v>
+        <v>201</v>
       </c>
       <c r="D54" t="n">
         <v>0</v>
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>148.9</v>
+        <v>172.2</v>
       </c>
       <c r="G54" t="n">
         <v>22</v>
@@ -2720,13 +2720,13 @@
         <v>11</v>
       </c>
       <c r="I54" t="n">
-        <v>170.9</v>
+        <v>194.2</v>
       </c>
       <c r="J54" t="n">
-        <v>170.9</v>
+        <v>194.2</v>
       </c>
       <c r="K54" t="n">
-        <v>170.9</v>
+        <v>194.2</v>
       </c>
       <c r="L54" t="n">
         <v>275</v>
@@ -2740,11 +2740,11 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>300</v>
+        <v>241</v>
       </c>
       <c r="D55" t="n">
         <v>0</v>
@@ -2753,7 +2753,7 @@
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>143.4</v>
+        <v>165.7</v>
       </c>
       <c r="G55" t="n">
         <v>22</v>
@@ -2762,13 +2762,13 @@
         <v>11</v>
       </c>
       <c r="I55" t="n">
-        <v>165.4</v>
+        <v>187.7</v>
       </c>
       <c r="J55" t="n">
-        <v>165.4</v>
+        <v>187.7</v>
       </c>
       <c r="K55" t="n">
-        <v>165.4</v>
+        <v>187.7</v>
       </c>
       <c r="L55" t="n">
         <v>275</v>
@@ -2777,16 +2777,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>160</v>
+        <v>250</v>
       </c>
       <c r="D56" t="n">
         <v>0</v>
@@ -2795,7 +2795,7 @@
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>243.9</v>
+        <v>161</v>
       </c>
       <c r="G56" t="n">
         <v>22</v>
@@ -2804,31 +2804,31 @@
         <v>11</v>
       </c>
       <c r="I56" t="n">
-        <v>265.9</v>
+        <v>183</v>
       </c>
       <c r="J56" t="n">
-        <v>265.9</v>
+        <v>183</v>
       </c>
       <c r="K56" t="n">
-        <v>265.9</v>
+        <v>183</v>
       </c>
       <c r="L56" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>177</v>
+        <v>300</v>
       </c>
       <c r="D57" t="n">
         <v>0</v>
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>234.5</v>
+        <v>156.5</v>
       </c>
       <c r="G57" t="n">
         <v>22</v>
@@ -2846,31 +2846,31 @@
         <v>11</v>
       </c>
       <c r="I57" t="n">
-        <v>256.5</v>
+        <v>178.5</v>
       </c>
       <c r="J57" t="n">
-        <v>256.5</v>
+        <v>178.5</v>
       </c>
       <c r="K57" t="n">
-        <v>256.5</v>
+        <v>178.5</v>
       </c>
       <c r="L57" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>201</v>
+        <v>153</v>
       </c>
       <c r="D58" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>226.1</v>
+        <v>191.5</v>
       </c>
       <c r="G58" t="n">
         <v>22</v>
@@ -2888,31 +2888,31 @@
         <v>11</v>
       </c>
       <c r="I58" t="n">
-        <v>248.1</v>
+        <v>213.5</v>
       </c>
       <c r="J58" t="n">
-        <v>248.1</v>
+        <v>213.5</v>
       </c>
       <c r="K58" t="n">
-        <v>248.1</v>
+        <v>213.5</v>
       </c>
       <c r="L58" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="D59" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>219.8</v>
+        <v>185.2</v>
       </c>
       <c r="G59" t="n">
         <v>22</v>
@@ -2930,31 +2930,31 @@
         <v>11</v>
       </c>
       <c r="I59" t="n">
-        <v>241.8</v>
+        <v>207.2</v>
       </c>
       <c r="J59" t="n">
-        <v>241.8</v>
+        <v>207.2</v>
       </c>
       <c r="K59" t="n">
-        <v>241.8</v>
+        <v>207.2</v>
       </c>
       <c r="L59" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>250</v>
+        <v>177</v>
       </c>
       <c r="D60" t="n">
         <v>0</v>
@@ -2963,7 +2963,7 @@
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>219.5</v>
+        <v>172.9</v>
       </c>
       <c r="G60" t="n">
         <v>22</v>
@@ -2972,31 +2972,31 @@
         <v>11</v>
       </c>
       <c r="I60" t="n">
-        <v>241.5</v>
+        <v>194.9</v>
       </c>
       <c r="J60" t="n">
-        <v>241.5</v>
+        <v>194.9</v>
       </c>
       <c r="K60" t="n">
-        <v>241.5</v>
+        <v>194.9</v>
       </c>
       <c r="L60" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>base</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="D61" t="n">
         <v>0</v>
@@ -3005,7 +3005,7 @@
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>219.5</v>
+        <v>162</v>
       </c>
       <c r="G61" t="n">
         <v>22</v>
@@ -3014,31 +3014,31 @@
         <v>11</v>
       </c>
       <c r="I61" t="n">
-        <v>241.5</v>
+        <v>184</v>
       </c>
       <c r="J61" t="n">
-        <v>241.5</v>
+        <v>184</v>
       </c>
       <c r="K61" t="n">
-        <v>241.5</v>
+        <v>184</v>
       </c>
       <c r="L61" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="D62" t="n">
         <v>0</v>
@@ -3047,7 +3047,7 @@
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>224.5</v>
+        <v>153.5</v>
       </c>
       <c r="G62" t="n">
         <v>22</v>
@@ -3056,31 +3056,31 @@
         <v>11</v>
       </c>
       <c r="I62" t="n">
-        <v>246.5</v>
+        <v>175.5</v>
       </c>
       <c r="J62" t="n">
-        <v>246.5</v>
+        <v>175.5</v>
       </c>
       <c r="K62" t="n">
-        <v>246.5</v>
+        <v>175.5</v>
       </c>
       <c r="L62" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>177</v>
+        <v>250</v>
       </c>
       <c r="D63" t="n">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>211.7</v>
+        <v>148.9</v>
       </c>
       <c r="G63" t="n">
         <v>22</v>
@@ -3098,31 +3098,31 @@
         <v>11</v>
       </c>
       <c r="I63" t="n">
-        <v>233.7</v>
+        <v>170.9</v>
       </c>
       <c r="J63" t="n">
-        <v>233.7</v>
+        <v>170.9</v>
       </c>
       <c r="K63" t="n">
-        <v>233.7</v>
+        <v>170.9</v>
       </c>
       <c r="L63" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MTL-TO</t>
+          <t>Ott-TO</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>reference-interne</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="D64" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>199.8</v>
+        <v>143.4</v>
       </c>
       <c r="G64" t="n">
         <v>22</v>
@@ -3140,16 +3140,16 @@
         <v>11</v>
       </c>
       <c r="I64" t="n">
-        <v>221.8</v>
+        <v>165.4</v>
       </c>
       <c r="J64" t="n">
-        <v>221.8</v>
+        <v>165.4</v>
       </c>
       <c r="K64" t="n">
-        <v>221.8</v>
+        <v>165.4</v>
       </c>
       <c r="L64" t="n">
-        <v>318</v>
+        <v>275</v>
       </c>
     </row>
     <row r="65">
@@ -3160,11 +3160,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>241</v>
+        <v>153</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -3173,7 +3173,7 @@
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>189.2</v>
+        <v>249</v>
       </c>
       <c r="G65" t="n">
         <v>22</v>
@@ -3182,13 +3182,13 @@
         <v>11</v>
       </c>
       <c r="I65" t="n">
-        <v>211.2</v>
+        <v>271</v>
       </c>
       <c r="J65" t="n">
-        <v>211.2</v>
+        <v>271</v>
       </c>
       <c r="K65" t="n">
-        <v>211.2</v>
+        <v>271</v>
       </c>
       <c r="L65" t="n">
         <v>318</v>
@@ -3202,11 +3202,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="D66" t="n">
         <v>0</v>
@@ -3215,7 +3215,7 @@
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>183.5</v>
+        <v>243.9</v>
       </c>
       <c r="G66" t="n">
         <v>22</v>
@@ -3224,13 +3224,13 @@
         <v>11</v>
       </c>
       <c r="I66" t="n">
-        <v>205.5</v>
+        <v>265.9</v>
       </c>
       <c r="J66" t="n">
-        <v>205.5</v>
+        <v>265.9</v>
       </c>
       <c r="K66" t="n">
-        <v>205.5</v>
+        <v>265.9</v>
       </c>
       <c r="L66" t="n">
         <v>318</v>
@@ -3244,11 +3244,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>pendulaire</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>300</v>
+        <v>177</v>
       </c>
       <c r="D67" t="n">
         <v>0</v>
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>176.1</v>
+        <v>234.5</v>
       </c>
       <c r="G67" t="n">
         <v>22</v>
@@ -3266,13 +3266,13 @@
         <v>11</v>
       </c>
       <c r="I67" t="n">
-        <v>198.1</v>
+        <v>256.5</v>
       </c>
       <c r="J67" t="n">
-        <v>198.1</v>
+        <v>256.5</v>
       </c>
       <c r="K67" t="n">
-        <v>198.1</v>
+        <v>256.5</v>
       </c>
       <c r="L67" t="n">
         <v>318</v>
@@ -3286,11 +3286,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="D68" t="n">
         <v>0</v>
@@ -3299,7 +3299,7 @@
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>220</v>
+        <v>226.1</v>
       </c>
       <c r="G68" t="n">
         <v>22</v>
@@ -3308,13 +3308,13 @@
         <v>11</v>
       </c>
       <c r="I68" t="n">
-        <v>242</v>
+        <v>248.1</v>
       </c>
       <c r="J68" t="n">
-        <v>242</v>
+        <v>248.1</v>
       </c>
       <c r="K68" t="n">
-        <v>242</v>
+        <v>248.1</v>
       </c>
       <c r="L68" t="n">
         <v>318</v>
@@ -3328,11 +3328,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>177</v>
+        <v>241</v>
       </c>
       <c r="D69" t="n">
         <v>0</v>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>204.1</v>
+        <v>219.8</v>
       </c>
       <c r="G69" t="n">
         <v>22</v>
@@ -3350,13 +3350,13 @@
         <v>11</v>
       </c>
       <c r="I69" t="n">
-        <v>226.1</v>
+        <v>241.8</v>
       </c>
       <c r="J69" t="n">
-        <v>226.1</v>
+        <v>241.8</v>
       </c>
       <c r="K69" t="n">
-        <v>226.1</v>
+        <v>241.8</v>
       </c>
       <c r="L69" t="n">
         <v>318</v>
@@ -3370,11 +3370,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>201</v>
+        <v>250</v>
       </c>
       <c r="D70" t="n">
         <v>0</v>
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>189.5</v>
+        <v>219.5</v>
       </c>
       <c r="G70" t="n">
         <v>22</v>
@@ -3392,13 +3392,13 @@
         <v>11</v>
       </c>
       <c r="I70" t="n">
-        <v>211.5</v>
+        <v>241.5</v>
       </c>
       <c r="J70" t="n">
-        <v>211.5</v>
+        <v>241.5</v>
       </c>
       <c r="K70" t="n">
-        <v>211.5</v>
+        <v>241.5</v>
       </c>
       <c r="L70" t="n">
         <v>318</v>
@@ -3412,11 +3412,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>base</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>241</v>
+        <v>300</v>
       </c>
       <c r="D71" t="n">
         <v>0</v>
@@ -3425,7 +3425,7 @@
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>176.9</v>
+        <v>219.5</v>
       </c>
       <c r="G71" t="n">
         <v>22</v>
@@ -3434,13 +3434,13 @@
         <v>11</v>
       </c>
       <c r="I71" t="n">
-        <v>198.9</v>
+        <v>241.5</v>
       </c>
       <c r="J71" t="n">
-        <v>198.9</v>
+        <v>241.5</v>
       </c>
       <c r="K71" t="n">
-        <v>198.9</v>
+        <v>241.5</v>
       </c>
       <c r="L71" t="n">
         <v>318</v>
@@ -3454,11 +3454,11 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>250</v>
+        <v>153</v>
       </c>
       <c r="D72" t="n">
         <v>0</v>
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>171.5</v>
+        <v>231.4</v>
       </c>
       <c r="G72" t="n">
         <v>22</v>
@@ -3476,13 +3476,13 @@
         <v>11</v>
       </c>
       <c r="I72" t="n">
-        <v>193.5</v>
+        <v>253.4</v>
       </c>
       <c r="J72" t="n">
-        <v>193.5</v>
+        <v>253.4</v>
       </c>
       <c r="K72" t="n">
-        <v>193.5</v>
+        <v>253.4</v>
       </c>
       <c r="L72" t="n">
         <v>318</v>
@@ -3496,11 +3496,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>reference-interne</t>
+          <t>pendulaire</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>300</v>
+        <v>160</v>
       </c>
       <c r="D73" t="n">
         <v>0</v>
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>162.9</v>
+        <v>224.5</v>
       </c>
       <c r="G73" t="n">
         <v>22</v>
@@ -3518,20 +3518,524 @@
         <v>11</v>
       </c>
       <c r="I73" t="n">
-        <v>184.9</v>
+        <v>246.5</v>
       </c>
       <c r="J73" t="n">
-        <v>184.9</v>
+        <v>246.5</v>
       </c>
       <c r="K73" t="n">
-        <v>184.9</v>
+        <v>246.5</v>
       </c>
       <c r="L73" t="n">
         <v>318</v>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>177</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" t="n">
+        <v>211.7</v>
+      </c>
+      <c r="G74" t="n">
+        <v>22</v>
+      </c>
+      <c r="H74" t="n">
+        <v>11</v>
+      </c>
+      <c r="I74" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="J74" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="K74" t="n">
+        <v>233.7</v>
+      </c>
+      <c r="L74" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>201</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0</v>
+      </c>
+      <c r="F75" t="n">
+        <v>199.8</v>
+      </c>
+      <c r="G75" t="n">
+        <v>22</v>
+      </c>
+      <c r="H75" t="n">
+        <v>11</v>
+      </c>
+      <c r="I75" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="J75" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="K75" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="L75" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>241</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" t="n">
+        <v>189.2</v>
+      </c>
+      <c r="G76" t="n">
+        <v>22</v>
+      </c>
+      <c r="H76" t="n">
+        <v>11</v>
+      </c>
+      <c r="I76" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="J76" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="K76" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="L76" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>250</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="G77" t="n">
+        <v>22</v>
+      </c>
+      <c r="H77" t="n">
+        <v>11</v>
+      </c>
+      <c r="I77" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="J77" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="K77" t="n">
+        <v>205.5</v>
+      </c>
+      <c r="L77" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>pendulaire</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>300</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="G78" t="n">
+        <v>22</v>
+      </c>
+      <c r="H78" t="n">
+        <v>11</v>
+      </c>
+      <c r="I78" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="J78" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>198.1</v>
+      </c>
+      <c r="L78" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>153</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" t="n">
+        <v>228.1</v>
+      </c>
+      <c r="G79" t="n">
+        <v>22</v>
+      </c>
+      <c r="H79" t="n">
+        <v>11</v>
+      </c>
+      <c r="I79" t="n">
+        <v>250.1</v>
+      </c>
+      <c r="J79" t="n">
+        <v>250.1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>250.1</v>
+      </c>
+      <c r="L79" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>160</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" t="n">
+        <v>220</v>
+      </c>
+      <c r="G80" t="n">
+        <v>22</v>
+      </c>
+      <c r="H80" t="n">
+        <v>11</v>
+      </c>
+      <c r="I80" t="n">
+        <v>242</v>
+      </c>
+      <c r="J80" t="n">
+        <v>242</v>
+      </c>
+      <c r="K80" t="n">
+        <v>242</v>
+      </c>
+      <c r="L80" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>177</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0</v>
+      </c>
+      <c r="F81" t="n">
+        <v>204.1</v>
+      </c>
+      <c r="G81" t="n">
+        <v>22</v>
+      </c>
+      <c r="H81" t="n">
+        <v>11</v>
+      </c>
+      <c r="I81" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="J81" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>226.1</v>
+      </c>
+      <c r="L81" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>201</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>22</v>
+      </c>
+      <c r="H82" t="n">
+        <v>11</v>
+      </c>
+      <c r="I82" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="J82" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="K82" t="n">
+        <v>211.5</v>
+      </c>
+      <c r="L82" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>241</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0</v>
+      </c>
+      <c r="F83" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="G83" t="n">
+        <v>22</v>
+      </c>
+      <c r="H83" t="n">
+        <v>11</v>
+      </c>
+      <c r="I83" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="J83" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="K83" t="n">
+        <v>198.9</v>
+      </c>
+      <c r="L83" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>250</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0</v>
+      </c>
+      <c r="F84" t="n">
+        <v>171.5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>22</v>
+      </c>
+      <c r="H84" t="n">
+        <v>11</v>
+      </c>
+      <c r="I84" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="J84" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="K84" t="n">
+        <v>193.5</v>
+      </c>
+      <c r="L84" t="n">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>MTL-TO</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>reference-interne</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>300</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0</v>
+      </c>
+      <c r="F85" t="n">
+        <v>162.9</v>
+      </c>
+      <c r="G85" t="n">
+        <v>22</v>
+      </c>
+      <c r="H85" t="n">
+        <v>11</v>
+      </c>
+      <c r="I85" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="J85" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="K85" t="n">
+        <v>184.9</v>
+      </c>
+      <c r="L85" t="n">
+        <v>318</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L73"/>
+  <autoFilter ref="A1:L85"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>